--- a/example[表格示例].xlsx
+++ b/example[表格示例].xlsx
@@ -4,19 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="898"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="898" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="3" r:id="rId1"/>
-    <sheet name="testArg_测试参数表" sheetId="16" r:id="rId2"/>
-    <sheet name="testKey_测试主键表" sheetId="19" r:id="rId3"/>
+    <sheet name="游戏参数表" sheetId="16" r:id="rId2"/>
+    <sheet name="道具" sheetId="33" r:id="rId3"/>
     <sheet name="技能类型表" sheetId="27" state="hidden" r:id="rId4"/>
-    <sheet name="testGroup_测试分组表" sheetId="25" r:id="rId5"/>
-    <sheet name="testArray_测试数组表" sheetId="30" r:id="rId6"/>
-    <sheet name="testSkill_技能" sheetId="32" r:id="rId7"/>
-    <sheet name="equipType_装备类型枚举" sheetId="35" r:id="rId8"/>
-    <sheet name="item_道具" sheetId="33" r:id="rId9"/>
-    <sheet name="equip_装备" sheetId="34" r:id="rId10"/>
+    <sheet name="装备" sheetId="34" r:id="rId5"/>
+    <sheet name="装备类型" sheetId="35" r:id="rId6"/>
+    <sheet name="成长类型" sheetId="25" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -85,7 +82,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="B6" authorId="0">
+    <comment ref="B5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -112,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="132">
   <si>
     <t>字段</t>
   </si>
@@ -159,10 +156,10 @@
     <t>注释</t>
   </si>
   <si>
-    <t>testArg</t>
+    <t>gameArg</t>
   </si>
   <si>
-    <t>测试参数表</t>
+    <t>游戏参数表</t>
   </si>
   <si>
     <t>YES</t>
@@ -171,52 +168,13 @@
     <t>参数表</t>
   </si>
   <si>
-    <t>testKey</t>
-  </si>
-  <si>
-    <t>测试主键表</t>
-  </si>
-  <si>
-    <t>主建表</t>
-  </si>
-  <si>
-    <t>testGroup</t>
-  </si>
-  <si>
-    <t>测试分组表</t>
-  </si>
-  <si>
-    <t>分组表</t>
-  </si>
-  <si>
-    <t>testArray</t>
-  </si>
-  <si>
-    <t>测试数组表</t>
-  </si>
-  <si>
-    <t>数组表</t>
-  </si>
-  <si>
-    <t>testSkill</t>
-  </si>
-  <si>
-    <t>技能</t>
-  </si>
-  <si>
-    <t>枚举</t>
-  </si>
-  <si>
-    <t>equipType</t>
-  </si>
-  <si>
-    <t>装备类型枚举</t>
-  </si>
-  <si>
     <t>item</t>
   </si>
   <si>
     <t>道具</t>
+  </si>
+  <si>
+    <t>主建表</t>
   </si>
   <si>
     <t>equip</t>
@@ -225,13 +183,22 @@
     <t>装备</t>
   </si>
   <si>
-    <t>testNo</t>
+    <t>equipType</t>
   </si>
   <si>
-    <t>测试不导出</t>
+    <t>装备类型</t>
   </si>
   <si>
-    <t>NO</t>
+    <t>枚举</t>
+  </si>
+  <si>
+    <t>growthType</t>
+  </si>
+  <si>
+    <t>成长类型</t>
+  </si>
+  <si>
+    <t>分组表</t>
   </si>
   <si>
     <t>符号</t>
@@ -255,219 +222,70 @@
     <t>值</t>
   </si>
   <si>
-    <t>选择种族范围，配置种族区间</t>
+    <t>游戏名字</t>
   </si>
   <si>
-    <t>raceScope</t>
+    <t>gameName</t>
   </si>
   <si>
-    <t>[]</t>
+    <t>string</t>
   </si>
   <si>
-    <t>[1,9]</t>
+    <t>我的世界</t>
   </si>
   <si>
-    <t>初始召唤币奖励</t>
+    <t>初始血量</t>
   </si>
   <si>
-    <t>initial</t>
-  </si>
-  <si>
-    <t>[1051,100]</t>
-  </si>
-  <si>
-    <t>召唤消耗配置</t>
-  </si>
-  <si>
-    <t>summonConsume</t>
-  </si>
-  <si>
-    <t>[1051,20]</t>
-  </si>
-  <si>
-    <t>召唤消耗成长系数</t>
-  </si>
-  <si>
-    <t>summonUPConsume</t>
+    <t>initHp</t>
   </si>
   <si>
     <t>number</t>
   </si>
   <si>
-    <t>场上最大存在怪物数</t>
+    <t>初始道具</t>
   </si>
   <si>
-    <t>monsterMax</t>
+    <t>initItems</t>
   </si>
   <si>
-    <t>随机稀有异兽概率</t>
+    <t>array&lt;example.item&gt;</t>
   </si>
   <si>
-    <t>random1</t>
+    <t>[1,2]</t>
   </si>
   <si>
-    <t>随机卓越异兽概率</t>
+    <t>id</t>
   </si>
   <si>
-    <t>random2</t>
-  </si>
-  <si>
-    <t>随机史诗异兽概率</t>
-  </si>
-  <si>
-    <t>random3</t>
-  </si>
-  <si>
-    <t>随机稀有异兽消耗</t>
-  </si>
-  <si>
-    <t>randomConsume1</t>
-  </si>
-  <si>
-    <t>[1052,1]</t>
-  </si>
-  <si>
-    <t>随机卓越异兽消耗</t>
-  </si>
-  <si>
-    <t>randomConsume2</t>
-  </si>
-  <si>
-    <t>随机史诗异兽消耗</t>
-  </si>
-  <si>
-    <t>randomConsume3</t>
-  </si>
-  <si>
-    <t>[1052,2]</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>测试</t>
-  </si>
-  <si>
-    <t>test</t>
+    <t>icon</t>
   </si>
   <si>
     <t>language</t>
   </si>
   <si>
-    <t>id</t>
+    <t>NO</t>
   </si>
   <si>
-    <t>atkRange</t>
+    <t>道具id</t>
   </si>
   <si>
-    <t>effect</t>
+    <t>道具名字</t>
   </si>
   <si>
-    <t>locationText</t>
+    <t>道具图标</t>
   </si>
   <si>
-    <t>summonPreview</t>
+    <t>道具1</t>
   </si>
   <si>
-    <t>数据校验</t>
+    <t>道具2</t>
   </si>
   <si>
-    <t>example.testGroup</t>
+    <t>道具3</t>
   </si>
   <si>
-    <t>example.testSkill</t>
-  </si>
-  <si>
-    <t>异兽id</t>
-  </si>
-  <si>
-    <t>异兽名字</t>
-  </si>
-  <si>
-    <t>成长类型</t>
-  </si>
-  <si>
-    <t>攻击范围</t>
-  </si>
-  <si>
-    <t>技能组</t>
-  </si>
-  <si>
-    <t>定位描述</t>
-  </si>
-  <si>
-    <t>合成预览</t>
-  </si>
-  <si>
-    <t>配置半径</t>
-  </si>
-  <si>
-    <t>[技能id，技能id2....]</t>
-  </si>
-  <si>
-    <t>异兽1</t>
-  </si>
-  <si>
-    <t>[1,2]</t>
-  </si>
-  <si>
-    <t>技能爆发流</t>
-  </si>
-  <si>
-    <t>异兽2</t>
-  </si>
-  <si>
-    <t>[3]</t>
-  </si>
-  <si>
-    <t>异兽3</t>
-  </si>
-  <si>
-    <t>异兽4</t>
+    <t>道具4</t>
   </si>
   <si>
     <t>注：</t>
@@ -503,6 +321,9 @@
     <t>单体子弹</t>
   </si>
   <si>
+    <t>[]</t>
+  </si>
+  <si>
     <t>飞行物AOE</t>
   </si>
   <si>
@@ -516,6 +337,9 @@
   </si>
   <si>
     <t>被动效果</t>
+  </si>
+  <si>
+    <t>技能</t>
   </si>
   <si>
     <t>[触发概率十万比]</t>
@@ -679,40 +503,13 @@
     <t>技能伤害</t>
   </si>
   <si>
-    <t>lv</t>
+    <t>gType</t>
   </si>
   <si>
-    <t>hp</t>
+    <t>example.equipType</t>
   </si>
   <si>
-    <t>def</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>companion</t>
-  </si>
-  <si>
-    <t>唯一id</t>
-  </si>
-  <si>
-    <t>技能名</t>
-  </si>
-  <si>
-    <t>技能id</t>
-  </si>
-  <si>
-    <t>技能1</t>
-  </si>
-  <si>
-    <t>技能2</t>
-  </si>
-  <si>
-    <t>技能3</t>
-  </si>
-  <si>
-    <t>技能4</t>
+    <t>example.growthType</t>
   </si>
   <si>
     <t>武器</t>
@@ -733,37 +530,16 @@
     <t>helmet</t>
   </si>
   <si>
-    <t>icon</t>
+    <t>lv</t>
   </si>
   <si>
-    <t>string</t>
+    <t>hp</t>
   </si>
   <si>
-    <t>道具id</t>
+    <t>def</t>
   </si>
   <si>
-    <t>道具名字</t>
-  </si>
-  <si>
-    <t>道具图标</t>
-  </si>
-  <si>
-    <t>道具1</t>
-  </si>
-  <si>
-    <t>道具2</t>
-  </si>
-  <si>
-    <t>道具3</t>
-  </si>
-  <si>
-    <t>道具4</t>
-  </si>
-  <si>
-    <t>example.equipType</t>
-  </si>
-  <si>
-    <t>装备类型</t>
+    <t>等级</t>
   </si>
 </sst>
 </file>
@@ -777,7 +553,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -787,13 +563,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -802,20 +578,6 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.05"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -843,25 +605,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1039,7 +782,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1060,6 +803,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="51"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1073,24 +828,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799951170384838"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799737540818506"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1311,7 +1048,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1322,9 +1061,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1457,301 +1194,281 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="3" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="2" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="7" fillId="9" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="9" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="3" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="9" fillId="10" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="10" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="3" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="3" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="53">
@@ -2093,7 +1810,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="28.875" customWidth="1"/>
@@ -2102,305 +1819,209 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="58" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58" t="s">
+      <c r="G1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="59"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="15" t="b">
+      <c r="A4" s="50" t="b">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
     </row>
     <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="15" t="b">
+      <c r="A5" s="50" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
     </row>
     <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="15" t="b">
+      <c r="A6" s="50" t="b">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="48"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:10">
+      <c r="A7" s="50" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:10">
-      <c r="A7" s="15" t="b">
+      <c r="C7" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:10">
+      <c r="A8" s="50" t="b">
         <v>1</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:10">
-      <c r="A8" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="60" t="s">
+      <c r="F8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
     </row>
     <row r="9" ht="16.5" spans="1:10">
-      <c r="A9" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" ht="16.5" spans="1:10">
-      <c r="A10" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:10">
-      <c r="A11" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="59"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:10">
-      <c r="A12" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="60"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:10">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:10">
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4 F5 F6 F7 F8">
       <formula1>"参数表,主建表,数组表,分组表,枚举"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2411,135 +2032,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
-  <cols>
-    <col min="3" max="3" width="35.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:4">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:4">
-      <c r="A8" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B8" s="8">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:4">
-      <c r="A9" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" s="8">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:4">
-      <c r="A10" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="类型错误" error="不支持的数据类型" sqref="B2 C2">
-      <formula1>"number,string,language,[],object"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B5 C4:C5">
-      <formula1>"YES,NO"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="5" max="5" width="19.375" customWidth="1"/>
@@ -2549,25 +2046,25 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:8">
       <c r="A1" s="9" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>7</v>
@@ -2581,34 +2078,45 @@
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:8">
+      <c r="A3" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="10"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:8">
-      <c r="A3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10"/>
     </row>
     <row r="4" ht="16.5" spans="1:8">
       <c r="A4" s="12" t="b">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>17</v>
@@ -2617,13 +2125,13 @@
         <v>17</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -2631,7 +2139,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>17</v>
@@ -2639,338 +2147,27 @@
       <c r="D5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>53</v>
+      <c r="E5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
-      <c r="A6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:8">
-      <c r="A7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="13">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:8">
-      <c r="A8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:8">
-      <c r="A9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="56">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:8">
-      <c r="A10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="56">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:8">
-      <c r="A11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="56">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:8">
-      <c r="A12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:8">
-      <c r="A13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B13" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:8">
-      <c r="A14" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B14" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:8">
-      <c r="A15" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="13">
-        <v>4.3</v>
-      </c>
-      <c r="H15" s="55"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:8">
-      <c r="A16" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="13">
-        <v>-1</v>
-      </c>
-      <c r="H16" s="55"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:8">
-      <c r="A17" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="13">
-        <v>1100</v>
-      </c>
-      <c r="H17" s="55"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:8">
-      <c r="A18" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:8">
-      <c r="A19" s="10" t="s">
+      <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E4">
+  <conditionalFormatting sqref="E1:E3">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="类型错误" error="不支持的数据类型" sqref="F4:F18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="类型错误" error="不支持的数据类型" sqref="F3:F4">
       <formula1>"number,string,language,[],object"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2983,398 +2180,165 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="4" max="4" width="19.5" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="6" width="31.25" customWidth="1"/>
-    <col min="7" max="8" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="13.875" customWidth="1"/>
+    <col min="4" max="4" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" ht="16.5" spans="1:5">
+      <c r="A1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="2" ht="16.5" spans="1:5">
+      <c r="A2" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:5">
+      <c r="A3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3" t="s">
+    </row>
+    <row r="4" ht="16.5" spans="1:5">
+      <c r="A4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>42</v>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:5">
+      <c r="A5" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:11">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:11">
-      <c r="A7" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:5">
+      <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:11">
-      <c r="A8" s="7" t="b">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:5">
+      <c r="A7" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="B8" s="8">
-        <v>101</v>
+      <c r="B7" s="19">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:5">
+      <c r="A8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" s="19">
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:5">
+      <c r="A9" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="E8">
-        <v>200</v>
-      </c>
-      <c r="F8" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H8">
-        <v>20604</v>
-      </c>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:11">
-      <c r="A9" s="7" t="b">
+      <c r="B9" s="19">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="B9" s="8">
-        <v>102</v>
-      </c>
-      <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9">
+    </row>
+    <row r="10" ht="16.5" spans="1:5">
+      <c r="A10" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" s="19">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10">
         <v>2</v>
       </c>
-      <c r="E9">
-        <v>200</v>
-      </c>
-      <c r="F9" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="G9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H9">
-        <v>20604</v>
-      </c>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:11">
-      <c r="A10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" s="8">
-        <v>103</v>
-      </c>
-      <c r="C10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>200</v>
-      </c>
-      <c r="F10" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="G10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10">
-        <v>20604</v>
-      </c>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:11">
-      <c r="A11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" s="8">
-        <v>104</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>200</v>
-      </c>
-      <c r="F11" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="G11" t="s">
-        <v>101</v>
-      </c>
-      <c r="H11">
-        <v>20604</v>
-      </c>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:11">
-      <c r="A12" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:11">
-      <c r="A13" s="7"/>
-      <c r="D13" s="54"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:11">
-      <c r="A14" s="7"/>
-      <c r="D14" s="54"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:11">
-      <c r="A15" s="7"/>
-      <c r="D15" s="54"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:11">
-      <c r="A16" s="7"/>
-      <c r="D16" s="54"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:4">
-      <c r="A17" s="7"/>
-      <c r="D17" s="54"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:4">
-      <c r="A18" s="7"/>
-      <c r="D18" s="54"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:4">
-      <c r="A19" s="7"/>
-      <c r="D19" s="54"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:4">
-      <c r="A20" s="7"/>
-      <c r="D20" s="54"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:4">
-      <c r="A21" s="7"/>
-      <c r="D21" s="54"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:4">
-      <c r="A22" s="7"/>
-      <c r="D22" s="54"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:4">
-      <c r="A23" s="7"/>
-      <c r="D23" s="54"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:4">
-      <c r="A24" s="7"/>
-      <c r="D24" s="54"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:4">
-      <c r="A25" s="7"/>
-      <c r="D25" s="54"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:4">
-      <c r="A26" s="7"/>
-      <c r="D26" s="54"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:4">
-      <c r="A27" s="7"/>
-      <c r="D27" s="54"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:4">
-      <c r="A28" s="7"/>
-      <c r="D28" s="54"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:4">
-      <c r="A29" s="7"/>
-      <c r="D29" s="54"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:4">
-      <c r="A30" s="7"/>
-      <c r="D30" s="54"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:4">
-      <c r="A31" s="7"/>
-      <c r="D31" s="54"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:4">
-      <c r="A32" s="7"/>
-      <c r="D32" s="54"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:4">
-      <c r="A33" s="7"/>
-      <c r="D33" s="54"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
+    </row>
+    <row r="11" ht="16.5" spans="1:5">
+      <c r="A11" s="18" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="类型错误" error="不支持的数据类型" sqref="B2 C2 D2:F2 G2:H2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="类型错误" error="不支持的数据类型" sqref="B2:D2">
       <formula1>"number,string,language,[],object"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B5 C4:C5 D4:F5 G4:H5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:D4">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -3387,1218 +2351,1218 @@
   <dimension ref="A3:AB54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="9" style="27"/>
-    <col min="3" max="3" width="55.125" style="27" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="27"/>
+    <col min="1" max="2" width="9" style="22"/>
+    <col min="3" max="3" width="55.125" style="22" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="22"/>
   </cols>
   <sheetData>
     <row r="3" ht="17.25" spans="1:22">
-      <c r="B3" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>107</v>
+      <c r="B3" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="17.25" spans="1:22">
-      <c r="B4" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" s="25" customFormat="1" ht="18" spans="1:22">
-      <c r="A7" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
+      <c r="B4" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" s="20" customFormat="1" ht="18" spans="1:22">
+      <c r="A7" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
+      <c r="A8" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="36">
+      <c r="A9" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="31">
         <v>1</v>
       </c>
-      <c r="C9" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33"/>
+      <c r="C9" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="38">
+      <c r="A10" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="33">
         <v>2</v>
       </c>
-      <c r="C10" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
+      <c r="C10" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="29"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" s="38">
+      <c r="A11" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="33">
         <v>3</v>
       </c>
-      <c r="C11" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
+      <c r="C11" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="29"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="35"/>
-      <c r="B12" s="38">
+      <c r="A12" s="30"/>
+      <c r="B12" s="33">
         <v>4</v>
       </c>
-      <c r="C12" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
+      <c r="C12" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
     </row>
     <row r="13" spans="1:22">
-      <c r="A13" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="39">
+      <c r="A13" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="34">
         <v>101</v>
       </c>
-      <c r="C13" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
+      <c r="C13" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="39">
+      <c r="A14" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="34">
         <v>102</v>
       </c>
-      <c r="C14" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
+      <c r="C14" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="39">
+      <c r="A15" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="34">
         <v>103</v>
       </c>
-      <c r="C15" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
+      <c r="C15" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="39">
+      <c r="A16" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="34">
         <v>104</v>
       </c>
-      <c r="C16" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
+      <c r="C16" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
     </row>
     <row r="17" spans="1:22">
-      <c r="A17" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="39">
+      <c r="A17" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="34">
         <v>105</v>
       </c>
-      <c r="C17" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
+      <c r="C17" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="41">
+      <c r="A18" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="36">
         <f>B13+10</f>
         <v>111</v>
       </c>
-      <c r="C18" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
+      <c r="C18" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="41">
+      <c r="A19" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="36">
         <f t="shared" ref="B19:B27" si="0">B14+10</f>
         <v>112</v>
       </c>
-      <c r="C19" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
+      <c r="C19" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="41">
+      <c r="A20" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="36">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="C20" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
+      <c r="C20" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="41">
+      <c r="A21" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="36">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="C21" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
+      <c r="C21" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
     </row>
     <row r="22" spans="1:22">
-      <c r="A22" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="41">
+      <c r="A22" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="36">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="C22" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
+      <c r="C22" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
     </row>
     <row r="23" spans="1:22">
-      <c r="A23" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="43">
+      <c r="A23" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="38">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="C23" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
+      <c r="C23" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="43">
+      <c r="A24" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="38">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
-      <c r="C24" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
+      <c r="C24" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
     </row>
     <row r="25" spans="1:22">
-      <c r="A25" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="43">
+      <c r="A25" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="38">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
-      <c r="C25" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
+      <c r="C25" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
     </row>
     <row r="26" spans="1:22">
-      <c r="A26" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="43">
+      <c r="A26" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="38">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="C26" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
+      <c r="C26" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
     </row>
     <row r="27" spans="1:22">
-      <c r="A27" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="43">
+      <c r="A27" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="38">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="C27" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
+      <c r="C27" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
     </row>
     <row r="28" spans="1:22">
-      <c r="A28" s="33"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
     </row>
     <row r="29" spans="1:22">
-      <c r="A29" s="33"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-    </row>
-    <row r="30" s="26" customFormat="1" spans="1:22">
-      <c r="A30" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="46"/>
-      <c r="P30" s="46"/>
-      <c r="Q30" s="46"/>
-      <c r="R30" s="46"/>
-      <c r="S30" s="46"/>
-      <c r="T30" s="46"/>
-      <c r="U30" s="46"/>
-      <c r="V30" s="46"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+    </row>
+    <row r="30" s="21" customFormat="1" spans="1:22">
+      <c r="A30" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
     </row>
     <row r="31" spans="1:22">
-      <c r="A31" s="47"/>
-      <c r="B31" s="31" t="s">
+      <c r="A31" s="42"/>
+      <c r="B31" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="A32" s="42"/>
+      <c r="B32" s="26">
+        <v>102</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+    </row>
+    <row r="33" spans="1:28">
+      <c r="A33" s="42"/>
+      <c r="B33" s="26">
+        <v>103</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="W33" s="44">
+        <v>102</v>
+      </c>
+      <c r="X33" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y33" s="44"/>
+    </row>
+    <row r="34" spans="1:28">
+      <c r="A34" s="42"/>
+      <c r="B34" s="26">
+        <v>104</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="W34" s="44">
+        <v>103</v>
+      </c>
+      <c r="X34" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y34" s="44"/>
+    </row>
+    <row r="35" spans="1:28">
+      <c r="A35" s="42"/>
+      <c r="B35" s="26">
+        <v>105</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="W35" s="44">
+        <v>104</v>
+      </c>
+      <c r="X35" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y35" s="44"/>
+    </row>
+    <row r="36" spans="1:28">
+      <c r="A36" s="42"/>
+      <c r="B36" s="26">
+        <v>106</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="W36" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="X36" s="44"/>
+      <c r="Y36" s="44"/>
+      <c r="Z36" s="44"/>
+      <c r="AA36" s="44"/>
+      <c r="AB36" s="44"/>
+    </row>
+    <row r="37" spans="1:28">
+      <c r="A37" s="42"/>
+      <c r="B37" s="26">
+        <v>107</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="W37" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="44"/>
+      <c r="Z37" s="44"/>
+      <c r="AA37" s="44"/>
+      <c r="AB37" s="44"/>
+    </row>
+    <row r="38" spans="1:28">
+      <c r="A38" s="45"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="W38" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="X38" s="44"/>
+      <c r="Y38" s="44"/>
+      <c r="Z38" s="44"/>
+      <c r="AA38" s="44"/>
+      <c r="AB38" s="44"/>
+    </row>
+    <row r="39" spans="1:28">
+      <c r="A39" s="28"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="W39" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="X39" s="44"/>
+      <c r="Y39" s="44"/>
+      <c r="Z39" s="44"/>
+      <c r="AA39" s="44"/>
+      <c r="AB39" s="44"/>
+    </row>
+    <row r="40" spans="1:28">
+      <c r="A40" s="28"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="W40" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="X40" s="44"/>
+      <c r="Y40" s="44"/>
+      <c r="Z40" s="44"/>
+      <c r="AA40" s="44"/>
+      <c r="AB40" s="44"/>
+    </row>
+    <row r="41" spans="1:28">
+      <c r="A41" s="28"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+      <c r="R41" s="28"/>
+      <c r="S41" s="28"/>
+      <c r="W41" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="X41" s="44"/>
+      <c r="Y41" s="44"/>
+      <c r="Z41" s="44"/>
+      <c r="AA41" s="44"/>
+      <c r="AB41" s="44"/>
+    </row>
+    <row r="42" spans="1:28">
+      <c r="A42" s="28"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="W42" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="X42" s="44"/>
+      <c r="Y42" s="44"/>
+      <c r="Z42" s="44"/>
+      <c r="AA42" s="44"/>
+      <c r="AB42" s="44"/>
+    </row>
+    <row r="43" spans="1:28">
+      <c r="A43" s="28"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="W43" s="46"/>
+      <c r="X43" s="44"/>
+      <c r="Y43" s="44"/>
+      <c r="Z43" s="44"/>
+      <c r="AA43" s="44"/>
+      <c r="AB43" s="44"/>
+    </row>
+    <row r="44" spans="1:28">
+      <c r="A44" s="28"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="28"/>
+      <c r="O44" s="28"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="28"/>
+      <c r="R44" s="28"/>
+      <c r="S44" s="28"/>
+      <c r="W44" s="46"/>
+      <c r="X44" s="44"/>
+      <c r="Y44" s="44"/>
+      <c r="Z44" s="44"/>
+      <c r="AA44" s="44"/>
+      <c r="AB44" s="44"/>
+    </row>
+    <row r="45" spans="1:28">
+      <c r="W45" s="46"/>
+      <c r="X45" s="46"/>
+      <c r="Y45" s="44"/>
+      <c r="Z45" s="44"/>
+      <c r="AA45" s="44"/>
+      <c r="AB45" s="44"/>
+    </row>
+    <row r="46" spans="1:28">
+      <c r="W46" s="46">
+        <v>1</v>
+      </c>
+      <c r="X46" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y46" s="44"/>
+      <c r="Z46" s="44"/>
+      <c r="AA46" s="44"/>
+      <c r="AB46" s="44"/>
+    </row>
+    <row r="47" spans="1:28">
+      <c r="W47" s="46">
+        <v>2</v>
+      </c>
+      <c r="X47" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="Y47" s="44"/>
+      <c r="Z47" s="44"/>
+      <c r="AA47" s="44"/>
+      <c r="AB47" s="44"/>
+    </row>
+    <row r="48" spans="1:28">
+      <c r="W48" s="46">
+        <v>3</v>
+      </c>
+      <c r="X48" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34" t="s">
+      <c r="Y48" s="44"/>
+      <c r="Z48" s="44"/>
+      <c r="AA48" s="44"/>
+      <c r="AB48" s="44"/>
+    </row>
+    <row r="49" spans="23:24">
+      <c r="W49" s="46">
+        <v>4</v>
+      </c>
+      <c r="X49" s="46" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="23:24">
+      <c r="W50" s="46">
+        <v>5</v>
+      </c>
+      <c r="X50" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="33"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="33"/>
-      <c r="S31" s="33"/>
-    </row>
-    <row r="32" spans="1:22">
-      <c r="A32" s="47"/>
-      <c r="B32" s="31">
-        <v>102</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="33"/>
-      <c r="R32" s="33"/>
-      <c r="S32" s="33"/>
-    </row>
-    <row r="33" spans="1:28">
-      <c r="A33" s="47"/>
-      <c r="B33" s="31">
-        <v>103</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="33"/>
-      <c r="W33" s="49">
-        <v>102</v>
-      </c>
-      <c r="X33" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y33" s="49"/>
-    </row>
-    <row r="34" spans="1:28">
-      <c r="A34" s="47"/>
-      <c r="B34" s="31">
-        <v>104</v>
-      </c>
-      <c r="C34" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="W34" s="49">
-        <v>103</v>
-      </c>
-      <c r="X34" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y34" s="49"/>
-    </row>
-    <row r="35" spans="1:28">
-      <c r="A35" s="47"/>
-      <c r="B35" s="31">
-        <v>105</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="33"/>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="33"/>
-      <c r="W35" s="49">
-        <v>104</v>
-      </c>
-      <c r="X35" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y35" s="49"/>
-    </row>
-    <row r="36" spans="1:28">
-      <c r="A36" s="47"/>
-      <c r="B36" s="31">
-        <v>106</v>
-      </c>
-      <c r="C36" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="W36" s="49" t="s">
-        <v>141</v>
-      </c>
-      <c r="X36" s="49"/>
-      <c r="Y36" s="49"/>
-      <c r="Z36" s="49"/>
-      <c r="AA36" s="49"/>
-      <c r="AB36" s="49"/>
-    </row>
-    <row r="37" spans="1:28">
-      <c r="A37" s="47"/>
-      <c r="B37" s="31">
-        <v>107</v>
-      </c>
-      <c r="C37" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33"/>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="33"/>
-      <c r="S37" s="33"/>
-      <c r="W37" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="X37" s="49"/>
-      <c r="Y37" s="49"/>
-      <c r="Z37" s="49"/>
-      <c r="AA37" s="49"/>
-      <c r="AB37" s="49"/>
-    </row>
-    <row r="38" spans="1:28">
-      <c r="A38" s="50"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="33"/>
-      <c r="N38" s="33"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
-      <c r="R38" s="33"/>
-      <c r="S38" s="33"/>
-      <c r="W38" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="X38" s="49"/>
-      <c r="Y38" s="49"/>
-      <c r="Z38" s="49"/>
-      <c r="AA38" s="49"/>
-      <c r="AB38" s="49"/>
-    </row>
-    <row r="39" spans="1:28">
-      <c r="A39" s="33"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33"/>
-      <c r="S39" s="33"/>
-      <c r="W39" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="X39" s="49"/>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-    </row>
-    <row r="40" spans="1:28">
-      <c r="A40" s="33"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="33"/>
-      <c r="N40" s="33"/>
-      <c r="O40" s="33"/>
-      <c r="P40" s="33"/>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="33"/>
-      <c r="S40" s="33"/>
-      <c r="W40" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="X40" s="49"/>
-      <c r="Y40" s="49"/>
-      <c r="Z40" s="49"/>
-      <c r="AA40" s="49"/>
-      <c r="AB40" s="49"/>
-    </row>
-    <row r="41" spans="1:28">
-      <c r="A41" s="33"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="33"/>
-      <c r="N41" s="33"/>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="33"/>
-      <c r="S41" s="33"/>
-      <c r="W41" s="49" t="s">
-        <v>152</v>
-      </c>
-      <c r="X41" s="49"/>
-      <c r="Y41" s="49"/>
-      <c r="Z41" s="49"/>
-      <c r="AA41" s="49"/>
-      <c r="AB41" s="49"/>
-    </row>
-    <row r="42" spans="1:28">
-      <c r="A42" s="33"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="33"/>
-      <c r="W42" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="X42" s="49"/>
-      <c r="Y42" s="49"/>
-      <c r="Z42" s="49"/>
-      <c r="AA42" s="49"/>
-      <c r="AB42" s="49"/>
-    </row>
-    <row r="43" spans="1:28">
-      <c r="A43" s="33"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33"/>
-      <c r="S43" s="33"/>
-      <c r="W43" s="51"/>
-      <c r="X43" s="49"/>
-      <c r="Y43" s="49"/>
-      <c r="Z43" s="49"/>
-      <c r="AA43" s="49"/>
-      <c r="AB43" s="49"/>
-    </row>
-    <row r="44" spans="1:28">
-      <c r="A44" s="33"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="33"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="33"/>
-      <c r="W44" s="51"/>
-      <c r="X44" s="49"/>
-      <c r="Y44" s="49"/>
-      <c r="Z44" s="49"/>
-      <c r="AA44" s="49"/>
-      <c r="AB44" s="49"/>
-    </row>
-    <row r="45" spans="1:28">
-      <c r="W45" s="51"/>
-      <c r="X45" s="51"/>
-      <c r="Y45" s="49"/>
-      <c r="Z45" s="49"/>
-      <c r="AA45" s="49"/>
-      <c r="AB45" s="49"/>
-    </row>
-    <row r="46" spans="1:28">
-      <c r="W46" s="51">
-        <v>1</v>
-      </c>
-      <c r="X46" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y46" s="49"/>
-      <c r="Z46" s="49"/>
-      <c r="AA46" s="49"/>
-      <c r="AB46" s="49"/>
-    </row>
-    <row r="47" spans="1:28">
-      <c r="W47" s="51">
-        <v>2</v>
-      </c>
-      <c r="X47" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y47" s="49"/>
-      <c r="Z47" s="49"/>
-      <c r="AA47" s="49"/>
-      <c r="AB47" s="49"/>
-    </row>
-    <row r="48" spans="1:28">
-      <c r="W48" s="51">
-        <v>3</v>
-      </c>
-      <c r="X48" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-    </row>
-    <row r="49" spans="23:24">
-      <c r="W49" s="51">
-        <v>4</v>
-      </c>
-      <c r="X49" s="51" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="50" spans="23:24">
-      <c r="W50" s="51">
-        <v>5</v>
-      </c>
-      <c r="X50" s="51" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="51" spans="23:24">
-      <c r="W51" s="51">
+      <c r="W51" s="46">
         <v>6</v>
       </c>
-      <c r="X51" s="51" t="s">
-        <v>160</v>
+      <c r="X51" s="46" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="23:24">
-      <c r="W52" s="51">
+      <c r="W52" s="46">
         <v>7</v>
       </c>
-      <c r="X52" s="51" t="s">
-        <v>161</v>
+      <c r="X52" s="46" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="23:24">
-      <c r="W53" s="51">
+      <c r="W53" s="46">
         <v>8</v>
       </c>
-      <c r="X53" s="51" t="s">
-        <v>162</v>
+      <c r="X53" s="46" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="23:24">
-      <c r="W54" s="51">
+      <c r="W54" s="46">
         <v>9</v>
       </c>
-      <c r="X54" s="51" t="s">
-        <v>163</v>
+      <c r="X54" s="46" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -4610,465 +3574,717 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2641"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="4" width="35.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" spans="1:5">
+      <c r="A1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:5">
+      <c r="A2" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:5">
+      <c r="A3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:5">
+      <c r="A4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:5">
+      <c r="A5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:5">
+      <c r="A6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:5">
+      <c r="A7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="19">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:5">
+      <c r="A8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" s="19">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:5">
+      <c r="A9" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="类型错误" error="不支持的数据类型" sqref="B2">
+      <formula1>"number,string,language,[],object"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 B3:C4">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="6"/>
+  <sheetData>
+    <row r="1" ht="16.5" spans="1:7">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:7">
+      <c r="A2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:7">
+      <c r="A3" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:7">
+      <c r="A4" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:7">
+      <c r="A5" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:7">
+      <c r="A6" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E1:E3">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2640"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="18.875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="11.375" style="17" customWidth="1"/>
-    <col min="4" max="4" width="18.75" style="17" customWidth="1"/>
-    <col min="5" max="5" width="9" style="17" customWidth="1"/>
+    <col min="2" max="2" width="18.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="A1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>59</v>
+      <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>400</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>600</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7">
+        <v>800</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1200</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6">
+        <v>6</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1400</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6">
+        <v>7</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1600</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" s="6">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="19" t="b">
+      <c r="D14" s="7">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B15" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C15" s="6">
+        <v>9</v>
+      </c>
+      <c r="D15" s="7">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="D8" s="13">
-        <v>400</v>
-      </c>
-      <c r="E8" s="13">
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6">
+        <v>10</v>
+      </c>
+      <c r="D16" s="7">
+        <v>2200</v>
+      </c>
+      <c r="E16" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="19" t="b">
+    <row r="17" spans="1:5">
+      <c r="A17" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B17" s="6">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="20">
+      <c r="D17" s="7">
+        <v>4600</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6">
         <v>2</v>
       </c>
-      <c r="D9" s="13">
-        <v>600</v>
-      </c>
-      <c r="E9" s="13">
+      <c r="C18" s="6">
+        <v>2</v>
+      </c>
+      <c r="D18" s="7">
+        <v>4800</v>
+      </c>
+      <c r="E18" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="19" t="b">
+    <row r="19" spans="1:5">
+      <c r="A19" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B19" s="6">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6">
+        <v>3</v>
+      </c>
+      <c r="D19" s="7">
+        <v>5000</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="C10" s="20">
-        <v>3</v>
-      </c>
-      <c r="D10" s="13">
-        <v>800</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="B20" s="6">
+        <v>2</v>
+      </c>
+      <c r="C20" s="6">
+        <v>4</v>
+      </c>
+      <c r="D20" s="7">
+        <v>5200</v>
+      </c>
+      <c r="E20" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="19" t="b">
+    <row r="21" spans="1:5">
+      <c r="A21" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B21" s="6">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6">
+        <v>5</v>
+      </c>
+      <c r="D21" s="7">
+        <v>5400</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="C11" s="20">
-        <v>4</v>
-      </c>
-      <c r="D11" s="13">
-        <v>1000</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="B22" s="6">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>6</v>
+      </c>
+      <c r="D22" s="7">
+        <v>5600</v>
+      </c>
+      <c r="E22" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="19" t="b">
+    <row r="23" spans="1:5">
+      <c r="A23" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B23" s="6">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>7</v>
+      </c>
+      <c r="D23" s="7">
+        <v>5800</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="C12" s="20">
-        <v>5</v>
-      </c>
-      <c r="D12" s="13">
-        <v>1200</v>
-      </c>
-      <c r="E12" s="13">
+      <c r="B24" s="6">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>8</v>
+      </c>
+      <c r="D24" s="7">
+        <v>6000</v>
+      </c>
+      <c r="E24" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="19" t="b">
+    <row r="25" spans="1:5">
+      <c r="A25" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B25" s="6">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6">
+        <v>9</v>
+      </c>
+      <c r="D25" s="7">
+        <v>6200</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="C13" s="20">
-        <v>6</v>
-      </c>
-      <c r="D13" s="13">
-        <v>1400</v>
-      </c>
-      <c r="E13" s="13">
+      <c r="B26" s="6">
+        <v>2</v>
+      </c>
+      <c r="C26" s="6">
+        <v>10</v>
+      </c>
+      <c r="D26" s="7">
+        <v>6400</v>
+      </c>
+      <c r="E26" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B14" s="20">
-        <v>1</v>
-      </c>
-      <c r="C14" s="20">
+    <row r="27" spans="1:5">
+      <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="13">
-        <v>1600</v>
-      </c>
-      <c r="E14" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" s="20">
-        <v>1</v>
-      </c>
-      <c r="C15" s="20">
-        <v>8</v>
-      </c>
-      <c r="D15" s="13">
-        <v>1800</v>
-      </c>
-      <c r="E15" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" s="20">
-        <v>1</v>
-      </c>
-      <c r="C16" s="20">
-        <v>9</v>
-      </c>
-      <c r="D16" s="13">
-        <v>2000</v>
-      </c>
-      <c r="E16" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" s="20">
-        <v>1</v>
-      </c>
-      <c r="C17" s="20">
-        <v>10</v>
-      </c>
-      <c r="D17" s="13">
-        <v>2200</v>
-      </c>
-      <c r="E17" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" s="20">
-        <v>2</v>
-      </c>
-      <c r="C18" s="20">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13">
-        <v>4600</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B19" s="20">
-        <v>2</v>
-      </c>
-      <c r="C19" s="20">
-        <v>2</v>
-      </c>
-      <c r="D19" s="13">
-        <v>4800</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B20" s="20">
-        <v>2</v>
-      </c>
-      <c r="C20" s="20">
-        <v>3</v>
-      </c>
-      <c r="D20" s="13">
-        <v>5000</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B21" s="20">
-        <v>2</v>
-      </c>
-      <c r="C21" s="20">
-        <v>4</v>
-      </c>
-      <c r="D21" s="13">
-        <v>5200</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B22" s="20">
-        <v>2</v>
-      </c>
-      <c r="C22" s="20">
-        <v>5</v>
-      </c>
-      <c r="D22" s="13">
-        <v>5400</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B23" s="20">
-        <v>2</v>
-      </c>
-      <c r="C23" s="20">
-        <v>6</v>
-      </c>
-      <c r="D23" s="13">
-        <v>5600</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B24" s="20">
-        <v>2</v>
-      </c>
-      <c r="C24" s="20">
-        <v>7</v>
-      </c>
-      <c r="D24" s="13">
-        <v>5800</v>
-      </c>
-      <c r="E24" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B25" s="20">
-        <v>2</v>
-      </c>
-      <c r="C25" s="20">
-        <v>8</v>
-      </c>
-      <c r="D25" s="13">
-        <v>6000</v>
-      </c>
-      <c r="E25" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B26" s="20">
-        <v>2</v>
-      </c>
-      <c r="C26" s="20">
-        <v>9</v>
-      </c>
-      <c r="D26" s="13">
-        <v>6200</v>
-      </c>
-      <c r="E26" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B27" s="20">
-        <v>2</v>
-      </c>
-      <c r="C27" s="20">
-        <v>10</v>
-      </c>
-      <c r="D27" s="13">
-        <v>6400</v>
-      </c>
-      <c r="E27" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="17" t="s">
-        <v>7</v>
-      </c>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+    </row>
+    <row r="28" ht="14.25" spans="1:5">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -5266,11 +4482,9 @@
       <c r="D60"/>
       <c r="E60"/>
     </row>
-    <row r="61" ht="14.25" spans="2:5">
+    <row r="61" spans="2:5">
       <c r="B61"/>
       <c r="C61"/>
-      <c r="D61"/>
-      <c r="E61"/>
     </row>
     <row r="62" spans="2:5">
       <c r="B62"/>
@@ -15587,10 +14801,6 @@
     <row r="2640" spans="2:3">
       <c r="B2640"/>
       <c r="C2640"/>
-    </row>
-    <row r="2641" spans="2:3">
-      <c r="B2641"/>
-      <c r="C2641"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -15602,863 +14812,4 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:7">
-      <c r="A1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:7">
-      <c r="A2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:7">
-      <c r="A3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:7">
-      <c r="A4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:7">
-      <c r="A6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:7">
-      <c r="A7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:7">
-      <c r="A8" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B8" s="20">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13">
-        <v>400</v>
-      </c>
-      <c r="D8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="21"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:7">
-      <c r="A9" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" s="20">
-        <v>2</v>
-      </c>
-      <c r="C9" s="13">
-        <v>600</v>
-      </c>
-      <c r="D9" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:7">
-      <c r="A10" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" s="20">
-        <v>3</v>
-      </c>
-      <c r="C10" s="13">
-        <v>800</v>
-      </c>
-      <c r="D10" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:7">
-      <c r="A11" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" s="20">
-        <v>4</v>
-      </c>
-      <c r="C11" s="13">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:7">
-      <c r="A12" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B12" s="20">
-        <v>5</v>
-      </c>
-      <c r="C12" s="13">
-        <v>1200</v>
-      </c>
-      <c r="D12" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B13" s="20">
-        <v>6</v>
-      </c>
-      <c r="C13" s="13">
-        <v>1400</v>
-      </c>
-      <c r="D13" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B14" s="20">
-        <v>7</v>
-      </c>
-      <c r="C14" s="13">
-        <v>1600</v>
-      </c>
-      <c r="D14" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" s="20">
-        <v>8</v>
-      </c>
-      <c r="C15" s="13">
-        <v>1800</v>
-      </c>
-      <c r="D15" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" s="20">
-        <v>9</v>
-      </c>
-      <c r="C16" s="13">
-        <v>2000</v>
-      </c>
-      <c r="D16" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" s="20">
-        <v>10</v>
-      </c>
-      <c r="C17" s="13">
-        <v>2200</v>
-      </c>
-      <c r="D17" s="13">
-        <v>0</v>
-      </c>
-      <c r="G17" s="22"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:7">
-      <c r="A18" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" s="20">
-        <v>11</v>
-      </c>
-      <c r="C18" s="13">
-        <v>2400</v>
-      </c>
-      <c r="D18" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:7">
-      <c r="A19" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B19" s="20">
-        <v>12</v>
-      </c>
-      <c r="C19" s="13">
-        <v>2600</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:7">
-      <c r="A20" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B20" s="20">
-        <v>13</v>
-      </c>
-      <c r="C20" s="13">
-        <v>2800</v>
-      </c>
-      <c r="D20" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:7">
-      <c r="A21" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B21" s="20">
-        <v>14</v>
-      </c>
-      <c r="C21" s="13">
-        <v>3000</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:7">
-      <c r="A22" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B22" s="20">
-        <v>15</v>
-      </c>
-      <c r="C22" s="13">
-        <v>3200</v>
-      </c>
-      <c r="D22" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:7">
-      <c r="A23" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B23" s="20">
-        <v>16</v>
-      </c>
-      <c r="C23" s="13">
-        <v>3400</v>
-      </c>
-      <c r="D23" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:7">
-      <c r="A24" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B24" s="20">
-        <v>17</v>
-      </c>
-      <c r="C24" s="13">
-        <v>3600</v>
-      </c>
-      <c r="D24" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:7">
-      <c r="A25" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B25" s="20">
-        <v>18</v>
-      </c>
-      <c r="C25" s="13">
-        <v>3800</v>
-      </c>
-      <c r="D25" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:7">
-      <c r="A26" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B26" s="20">
-        <v>19</v>
-      </c>
-      <c r="C26" s="13">
-        <v>4000</v>
-      </c>
-      <c r="D26" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:7">
-      <c r="A27" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B27" s="20">
-        <v>20</v>
-      </c>
-      <c r="C27" s="13">
-        <v>4200</v>
-      </c>
-      <c r="D27" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:7">
-      <c r="A28" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B28" s="20">
-        <v>21</v>
-      </c>
-      <c r="C28" s="13">
-        <v>4400</v>
-      </c>
-      <c r="D28" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:7">
-      <c r="A29" s="17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="类型错误" error="不支持的数据类型" sqref="B2:D2">
-      <formula1>"number,string,language,[],object"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
-  <cols>
-    <col min="2" max="2" width="15.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:4">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:4">
-      <c r="A8" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B8" s="8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:4">
-      <c r="A9" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" s="8">
-        <v>2</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:4">
-      <c r="A10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" s="8">
-        <v>3</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:4">
-      <c r="A11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" s="8">
-        <v>4</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:4">
-      <c r="A12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="16"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="C12">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8:C11">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="类型错误" error="不支持的数据类型" sqref="B2:C2">
-      <formula1>"number,string,language,[],object"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C5">
-      <formula1>"YES,NO"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="6"/>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:7">
-      <c r="A1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:7">
-      <c r="A2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="10"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:7">
-      <c r="A3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:7">
-      <c r="A4" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:7">
-      <c r="A5" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="F5" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:7">
-      <c r="A6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:7">
-      <c r="A7" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="E1:E4">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:5">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
-      <c r="A8" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B8" s="8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
-      <c r="A9" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" s="8">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>188</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:5">
-      <c r="A10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" s="8">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:5">
-      <c r="A11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" s="8">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:5">
-      <c r="A12" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="类型错误" error="不支持的数据类型" sqref="B2 C2 D2">
-      <formula1>"number,string,language,[],object"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B5 C4:C5 D4:D5">
-      <formula1>"YES,NO"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>